--- a/output/roomself_excel/5093.xlsx
+++ b/output/roomself_excel/5093.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>197730</v>
+        <v>176198</v>
       </c>
       <c r="D2" t="n">
-        <v>3588</v>
+        <v>5076</v>
       </c>
       <c r="E2" t="n">
-        <v>543</v>
+        <v>435</v>
       </c>
       <c r="F2" t="n">
-        <v>434</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>276279</v>
+        <v>11776</v>
       </c>
       <c r="D3" t="n">
-        <v>4384</v>
+        <v>880</v>
       </c>
       <c r="E3" t="n">
-        <v>703</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>197739</v>
+        <v>11132</v>
       </c>
       <c r="D4" t="n">
-        <v>3600</v>
+        <v>852</v>
       </c>
       <c r="E4" t="n">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>361041</v>
+        <v>52632</v>
       </c>
       <c r="D5" t="n">
-        <v>5000</v>
+        <v>1848</v>
       </c>
       <c r="E5" t="n">
-        <v>880</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>482</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>109668</v>
+        <v>108665</v>
       </c>
       <c r="D6" t="n">
-        <v>3436</v>
+        <v>2996</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>193674</v>
+        <v>5141</v>
       </c>
       <c r="D7" t="n">
-        <v>3556</v>
+        <v>600</v>
       </c>
       <c r="E7" t="n">
-        <v>542</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>426</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>176198</v>
+        <v>18480</v>
       </c>
       <c r="D8" t="n">
-        <v>5076</v>
+        <v>1108</v>
       </c>
       <c r="E8" t="n">
-        <v>435</v>
+        <v>165</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108665</v>
+        <v>197730</v>
       </c>
       <c r="D9" t="n">
-        <v>2996</v>
+        <v>3588</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>543</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11776</v>
+        <v>276279</v>
       </c>
       <c r="D10" t="n">
-        <v>880</v>
+        <v>4384</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>703</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11132</v>
+        <v>197739</v>
       </c>
       <c r="D11" t="n">
-        <v>852</v>
+        <v>3600</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10044</v>
+        <v>361041</v>
       </c>
       <c r="D12" t="n">
-        <v>820</v>
+        <v>5000</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>52632</v>
+        <v>109668</v>
       </c>
       <c r="D13" t="n">
-        <v>1848</v>
+        <v>3436</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4081</v>
+        <v>193674</v>
       </c>
       <c r="D14" t="n">
-        <v>520</v>
+        <v>3556</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>542</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5141</v>
+        <v>10044</v>
       </c>
       <c r="D15" t="n">
-        <v>600</v>
+        <v>820</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4399</v>
+        <v>4081</v>
       </c>
       <c r="D16" t="n">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F16" t="n">
         <v>29</v>
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>76581</v>
+        <v>4399</v>
       </c>
       <c r="D17" t="n">
-        <v>2252</v>
+        <v>544</v>
       </c>
       <c r="E17" t="n">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>275</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13728</v>
+        <v>76581</v>
       </c>
       <c r="D18" t="n">
-        <v>956</v>
+        <v>2252</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>39954</v>
+        <v>13728</v>
       </c>
       <c r="D19" t="n">
-        <v>1936</v>
+        <v>956</v>
       </c>
       <c r="E19" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18480</v>
+        <v>39954</v>
       </c>
       <c r="D20" t="n">
-        <v>1108</v>
+        <v>1936</v>
       </c>
       <c r="E20" t="n">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5093.xlsx
+++ b/output/roomself_excel/5093.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>5076</v>
       </c>
-      <c r="E2" t="n">
-        <v>435</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,12 @@
       <c r="D3" t="n">
         <v>880</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +547,12 @@
       <c r="D4" t="n">
         <v>852</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +569,20 @@
       <c r="D5" t="n">
         <v>1848</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>70</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>23</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +599,12 @@
       <c r="D6" t="n">
         <v>2996</v>
       </c>
-      <c r="E6" t="n">
-        <v>153</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +621,20 @@
       <c r="D7" t="n">
         <v>600</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>97</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>29</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +651,20 @@
       <c r="D8" t="n">
         <v>1108</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>165</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>23</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +681,27 @@
       <c r="D9" t="n">
         <v>3588</v>
       </c>
-      <c r="E9" t="n">
-        <v>543</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>434</v>
+        <v>483</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>377</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +719,20 @@
       <c r="D10" t="n">
         <v>4384</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>703</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>29</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +749,20 @@
       <c r="D11" t="n">
         <v>3600</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>519</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>29</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +779,27 @@
       <c r="D12" t="n">
         <v>5000</v>
       </c>
-      <c r="E12" t="n">
-        <v>880</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>482</v>
+        <v>872</v>
+      </c>
+      <c r="G12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>770</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +817,12 @@
       <c r="D13" t="n">
         <v>3436</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +839,27 @@
       <c r="D14" t="n">
         <v>3556</v>
       </c>
-      <c r="E14" t="n">
-        <v>542</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>426</v>
+        <v>370</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>482</v>
+      </c>
+      <c r="J14" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +877,12 @@
       <c r="D15" t="n">
         <v>820</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +899,20 @@
       <c r="D16" t="n">
         <v>520</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>77</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>29</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +929,20 @@
       <c r="D17" t="n">
         <v>544</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>83</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>29</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,11 +959,27 @@
       <c r="D18" t="n">
         <v>2252</v>
       </c>
-      <c r="E18" t="n">
-        <v>329</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>275</v>
+        <v>306</v>
+      </c>
+      <c r="G18" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>252</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -849,12 +997,12 @@
       <c r="D19" t="n">
         <v>956</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,11 +1019,27 @@
       <c r="D20" t="n">
         <v>1936</v>
       </c>
-      <c r="E20" t="n">
-        <v>281</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>249</v>
+        <v>226</v>
+      </c>
+      <c r="G20" t="n">
+        <v>23</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>258</v>
+      </c>
+      <c r="J20" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
